--- a/backend/data/raw/qiaopi_213_text.xlsx
+++ b/backend/data/raw/qiaopi_213_text.xlsx
@@ -410,7 +410,7 @@
       </c>
       <c r="D2" s="12" t="inlineStr">
         <is>
-          <t>辛 (1911) 阳月 (十月) 初十日, 越南薛孝居寄海邑西洋鄉張捷謙少分</t>
+          <t>辛（1911）阳月（十月）初十日，越南薛老居寄海邑西洋乡张捷谦少爷</t>
         </is>
       </c>
       <c r="E2" s="12" t="inlineStr">
@@ -467,7 +467,7 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>辛 (1921) 十一月初四，助坡 [新加坡] 林序周寄潮安大寨家双亲大人</t>
+          <t>辛（1921）十一月初四，叻坡［新加坡］林序周寄潮安大寨家双亲大人</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
@@ -524,7 +524,7 @@
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
-          <t>民国十三年 (1924) 五月八號, 呈 [新加坡] 林序周寄潮安大寨家父亲大人</t>
+          <t>民国十三年（1924）五月八号，叻［新加坡］林序周寄潮安大寨家父亲大人</t>
         </is>
       </c>
       <c r="E4" s="12" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>丙年(1926) 八月廿六日，外洋儿贞寄潮汕慈亲大人</t>
+          <t>丙年（1926）八月廿六日，外洋儿贞寄潮汕慈亲大人</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>内 (1927) 十二月十一日, 越[沙擋越」陳進保寄澄邑程洋貞家大嫂</t>
+          <t>丙（1927）十二月十一日，越［沙捞越］陈进保寄澄邑程洋冈家大嫂</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>丁 (1927) 九月初五日，外洋两锋寄潮汕花灯大人</t>
+          <t>丁（1927）九月初五日，外洋两猛寄潮汕慈亲大人</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>成 (1928) 六月十七, 进 [泰国] 圣源寄洒 (湾) 邑南砂乡林严灯大人</t>
+          <t>戊（1928）六月十七，暹［泰国］圣源寄汀（澄）邑南砂乡林严亲大人</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>戊 (1928) 七月十六日, 外洋西猛寄潮汕慈親大人</t>
+          <t>戊（1928）七月十六日，外洋两猛寄潮汕慈亲大人</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>己 (1929) 七月廿五日，(进] 大弟寄(洪连中余宅]荆妻李氏</t>
+          <t>己（1929）七月廿五日，［暹］大弟寄［澄莲中余宅］荆妻李氏</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>十八年 (1929) 十月十三日，外洋上页玉寄潮汕花灯大人</t>
+          <t>十八年（1929）十月十三日，外洋贞玉寄潮汕慈亲大人</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>庚年(1930) 三月初八日，彭享 [马来亚] 刘仕芝寄潮安东风乡陈赞堂先生</t>
+          <t>庚年（1930）三月初八日，彭亨［马来亚］刘仕芝寄潮安东凤乡陈赞堂先生</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>辛末(1931) 四月三十日, 肋吳錦興寄潮安江東都洪金祝先生</t>
+          <t>辛未（1931）四月三十日，叻吴锦兴寄潮安江东都洪金祝先生</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>至(1931) 七月十六日，进何春好寄潮吧何讶围乡家母亲大人</t>
+          <t>辛（1931）七月十六日，暹何春好寄潮邑何厝围乡家母亲大人</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>千 (1932) 三月十七，进刘寿春寄漆邑月窒内乡家母洒大人</t>
+          <t>壬（1932）三月十七，暹刘寿春寄澄海月窟内乡家母亲大人</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>千 (1932) 三月廿日，外洋陈公寄潮汕媳妇</t>
+          <t>壬（1932）三月廿日，外洋陈公寄潮汕媳妇</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>千申年 (1932) 六月十一日，外洋大专寄潮汕祖父大人</t>
+          <t>壬申年（1932）六月十一日，外洋大专寄潮汕祖父大人</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>發 (1933) 九月十一日, 越姚丁南寄潮安南桂家母親大人</t>
+          <t>癸（1933）九月十一日，越姚丁南寄潮安南桂家母亲大人</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>民国廿三年 (1934) 元月初五日, 外洋曾大專寄潮汕祖父大人</t>
+          <t>民国廿三年（1934）元月初五日，外洋曾大专寄潮汕祖父大人</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>甲 (1934) 五月初八日, 呷[馬來亞呷坡]」 林松漢寄潮汕家榮果兄台</t>
+          <t>甲（1934）五月初八日，呷［马来亚呷坡］林松汉寄潮汕家荣泉兄台</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>民二十三年 (1935) 旧历十二月初二日，</t>
+          <t>民二十三年（1935）旧历十二月初二日，房亨［马来亚彭亨］北根陈集良寄潮安东凤乡陈赞堂先生</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>十四年 (1935) 六月三号，外洋南山寄潮汕父亲大人</t>
+          <t>廿四年（1935）六月三号，外洋南山寄潮汕父亲大人</t>
         </is>
       </c>
       <c r="E22" s="12" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>廿四年(1935) 九月十四号，进京许卓峰寄饶色隆都家祖母大人</t>
+          <t>廿四年（1935）九月十四号，暹京许卓峰寄饶邑隆都家祖母大人</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>中华民国廿四年 (1935) 十一月十三日，进镇辊寄馈平隆都吴宅双亲大人</t>
+          <t>中华民国廿四年（1935）十一月十三日，暹镇乾寄饶平隆都吴宅双亲大人</t>
         </is>
       </c>
       <c r="E24" s="12" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>乙冀年 (1935) 十月廿二日，进财福寄汀 (湾) 即南砂乡林宅慈亲大人</t>
+          <t>乙亥年（1935）十月廿二日，暹财福寄汀（澄）邑南砂乡林宅慈亲大人</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>中华民国乙年 (1935) 二月州日，外洋永源寄潮汕大兄</t>
+          <t>中华民国乙年（1935）十月廿日，外洋永源寄潮汕大兄</t>
         </is>
       </c>
       <c r="E26" s="12" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>甲七月初五日 (1936 前) ，外洋林荣果寄潮汕朝晋胞弟</t>
+          <t>甲七月初五日（1936前），外洋林荣泉寄潮汕朝晋胞弟</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>甲九月廿五日 (1936 前),，[进] 大弟寄〔溢莲中余宅]荆帮李氏</t>
+          <t>甲九月廿五日（1936前），［暹］大弟寄［澄莲中余宅］荆妻李氏</t>
         </is>
       </c>
       <c r="E28" s="12" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>乙四月初五日 (1936 前)，外洋丘明正寄潮汕岳祖母、岳慈亲</t>
+          <t>乙四月初五日（1936前），外洋丘明正寄潮汕岳祖母、岳慈亲</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>乙六月初八日 (1936 前), 越陳國保寄澄邑程洋崗家慈親老大人</t>
+          <t>乙六月初八日（1936前），越陈国保寄澄邑程洋冈家慈亲老大人</t>
         </is>
       </c>
       <c r="E30" s="12" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>庚七月十九日 (1936 前)，进大弟寄滋莲中余宅荆麦李氏</t>
+          <t>庚七月十九日（1936前），暹大弟寄澄莲中余宅荆妻李氏</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>庚完月(十二月) 十二日 (1936 前), 外洋李來盛寄潮汕大姊</t>
+          <t>庚完月（十二月）十二日（1936前），外洋李来盛寄潮汕大姊</t>
         </is>
       </c>
       <c r="E32" s="12" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>辛七月初七日 (1936 前)，外洋陈进保寄潮汕花灯大人</t>
+          <t>辛七月初七日（1936前），外洋陈进保寄潮汕慈亲大人</t>
         </is>
       </c>
       <c r="E33" s="12" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>傾十月十五日 (1936 前) ，进来镇寄潮安巷塘乡刘氏贤妻</t>
+          <t>癸十月廿五日（1936前），暹来镇寄潮安鹤塘乡刘氏贤妻</t>
         </is>
       </c>
       <c r="E34" s="12" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>二月初八日 (1936 前)，进大专寄洒 (澄) 邑中外區家祖父大人</t>
+          <t>二月初八日（1936前），暹大专寄汀（澄）邑中外区家祖父大人</t>
         </is>
       </c>
       <c r="E35" s="12" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>七月四日 (1936 前)，外洋许美禾寄潮汕母兴大人</t>
+          <t>七月四日（1936前），外洋什美馥寄潮汕母亲大人</t>
         </is>
       </c>
       <c r="E36" s="12" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>八月初一(1936 前)，麻坡 [马来亚] 陳弟咱寄潮安東風家綿浩胞兄</t>
+          <t>八月初一（1936前），麻坡［马来亚］陈弟阵寄潮安东凤家绵浩胞兄</t>
         </is>
       </c>
       <c r="E37" s="12" t="inlineStr">
@@ -2320,7 +2320,7 @@
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>八月廿五日 (1936 前) ，外洋雄才寄潮汕母亲大人</t>
+          <t>八月廿五日（1936前），外洋雄才寄潮汕母亲大人</t>
         </is>
       </c>
       <c r="E38" s="12" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>十月初六日 (1936 前)，号曾清鉴寄潮安凤廓新乡郭财和先生</t>
+          <t>十月初六日（1936前），叻曾清鉴寄潮安凤廓新乡郭财和先生</t>
         </is>
       </c>
       <c r="E39" s="12" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>阳月(十月) 十七日 (1936 前) ,号陈喜炎寄潮安东风乡陈镇炎胞兄</t>
+          <t>阳月（十月）十七日（1936前），叻陈喜炎寄潮安东凤乡陈镇炎胞兄</t>
         </is>
       </c>
       <c r="E40" s="12" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>图月甘一日 (1936 前)，外洋男寄潮汕母兴大人</t>
+          <t>闰月廿一日（1936前），外洋男寄潮汕母亲大人</t>
         </is>
       </c>
       <c r="E41" s="12" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>(1936 前) 叻李開源寄潮安急水陳振平賢复</t>
+          <t>（1936前）叻李开源寄潮安急水陈振平贤婿</t>
         </is>
       </c>
       <c r="E42" s="12" t="inlineStr">
@@ -2567,7 +2567,7 @@
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>廿五年 (1936) 元月初七日，外洋大才寄潮汕祖父大人</t>
+          <t>廿五年（1936）元月初七日，外洋大才寄潮汕祖父大人</t>
         </is>
       </c>
       <c r="E43" s="12" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>到 (1936) 六月廿日，外洋大专寄潮汕祖父大人</t>
+          <t>丙（1936）六月廿日，外洋大专寄潮汕祖父大人</t>
         </is>
       </c>
       <c r="E44" s="12" t="inlineStr">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>丙(1936) 六月廿四日，外洋丁南寄潮汕母亲大人</t>
+          <t>丙（1936）六月廿四日，外洋丁南寄潮汕母亲大人</t>
         </is>
       </c>
       <c r="E45" s="12" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>十五年 (1936) 六月廿六，进卓峰寄饶邑降都许双亲大人</t>
+          <t>廿五年（1936）六月廿六，暹卓峰寄饶邑隆都许双亲大人</t>
         </is>
       </c>
       <c r="E46" s="12" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>十五年 (1936) 七月五日，外洋程兴寄潮汕双亲大人</t>
+          <t>廿五年（1936）七月五日，外洋程兴寄潮汕双亲大人</t>
         </is>
       </c>
       <c r="E47" s="12" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>丙年 (1936) 七月廿四日，嘻哼 (绢享) 陈赞堂寄潮安东风乡家祖苹大人</t>
+          <t>丙年（1936）七月廿四日，咏亨（彭亨）陈赞堂寄潮安东凤乡家祖母大人</t>
         </is>
       </c>
       <c r="E48" s="12" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>两子年(1936) 七月廿五日，外洋再炎寄潮汕外祖母大人</t>
+          <t>丙子年（1936）七月廿五日，外洋再火寄潮汕外祖母大人</t>
         </is>
       </c>
       <c r="E49" s="12" t="inlineStr">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>十五年 (1936) 十一月十九，外洋程兴寄潮汕双亲大人</t>
+          <t>廿五年（1936）十一月十九，外洋程兴寄潮汕双亲大人</t>
         </is>
       </c>
       <c r="E50" s="12" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>廿六年 (1937) 元月十一號, 外洋文高寄潮汕母親大人</t>
+          <t>廿六年（1937）元月十二号，外洋文高寄潮汕母亲大人</t>
         </is>
       </c>
       <c r="E51" s="12" t="inlineStr">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>十六年 (1937) 二月三日，外洋清容寄潮汕余氏贤妻</t>
+          <t>廿六年（1937）二月三日，外洋清裕寄潮汕余氏贤妻</t>
         </is>
       </c>
       <c r="E52" s="12" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>廿六年 (1937) 八月初六日, 叻林思頁寄澄海程洋貞林思敬先生</t>
+          <t>廿六年（1937）八月初六日，叻林思贞寄澄海程洋冈林思敬先生</t>
         </is>
       </c>
       <c r="E53" s="12" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>丁 (1937) 八月二十日，潮安稚塘乡光裕寄进陈运异父亲大人</t>
+          <t>丁（1937）八月二十日，潮安鹤塘乡光裕寄暹陈运昇父亲大人</t>
         </is>
       </c>
       <c r="E54" s="12" t="inlineStr">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>中华民国廿六年(1937) 十一月廿六日，外洋义林宕潮汕壮城表兄台</t>
+          <t>中华民国廿六年（1937）十一月廿六日，外洋义林寄潮汕壮城表兄台</t>
         </is>
       </c>
       <c r="E55" s="12" t="inlineStr">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>丁丑年(1937) 十一月甘七日，外洋陈继源寄潮汕巡母大人</t>
+          <t>丁丑年（1937）十一月廿七日，外洋陈继源寄潮汕姆母大人</t>
         </is>
       </c>
       <c r="E56" s="12" t="inlineStr">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>本姑 (1938) 完月 (十二月) 初四日，号陈赞名寄溢邑程洋岗林思散先生</t>
+          <t>丁丑（1938）完月（十二月）初四日，叻陈赞名寄澄邑程洋冈林思敬先生</t>
         </is>
       </c>
       <c r="E57" s="12" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>成 (1938) 三月初五日，外洋继豪寄潮汕母亲</t>
+          <t>戊（1938）三月初五日，外洋继豪寄潮汕母亲</t>
         </is>
       </c>
       <c r="E58" s="12" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>成 (1938) 五月初四日，外洋丁炳南寄潮汕岳母大人</t>
+          <t>戊（1938）五月初四日，外洋丁炳南寄潮汕岳母大人</t>
         </is>
       </c>
       <c r="E59" s="12" t="inlineStr">
@@ -3413,7 +3413,7 @@
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>成 (1938) 五月十五日，进财福寄湾邑南砂乡林宅慈亲大人</t>
+          <t>戊（1938）五月十五日，暹财福寄澄邑南砂乡林宅慈亲大人</t>
         </is>
       </c>
       <c r="E60" s="12" t="inlineStr">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>成 (1938) 五月甘七日，呈宋树钊寄溢邑下连家双亲大人</t>
+          <t>戊（1938）五月廿七日，叻宋树钊寄澄邑下蓬家双亲大人</t>
         </is>
       </c>
       <c r="E61" s="12" t="inlineStr">
@@ -3530,7 +3530,7 @@
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>成 (1938) 六月十五日, 香 [香港] 活兆祥寄饒吧百砂鄉家祖慈大人</t>
+          <t>戊（1938）六月十五日，香［香港］潘兆祥寄饶邑碧砂乡家祖慈大人</t>
         </is>
       </c>
       <c r="E62" s="12" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>成 (1938) 六月廿九日，外洋万乘寄潮汕塘氏贤妻</t>
+          <t>戊（1938）六月廿九日，外洋万乘寄潮汕塘氏贤妻</t>
         </is>
       </c>
       <c r="E63" s="12" t="inlineStr">
@@ -3643,7 +3643,7 @@
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>成 (1938) 七月初十日, 還海果寄饒隆南溪鄉趁宅慈親大人</t>
+          <t>戊（1938）七月初十日，暹海泉寄饶隆南溪乡赵宅慈亲大人</t>
         </is>
       </c>
       <c r="E64" s="12" t="inlineStr">
@@ -3700,7 +3700,7 @@
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>成 (1938) 桂月 (八月) 廿日，越丁南寄潮安南桂都姚庆松吾儿</t>
+          <t>戊（1938）桂月（八月）廿日，越丁南寄潮安南桂都姚庆松吾儿</t>
         </is>
       </c>
       <c r="E65" s="12" t="inlineStr">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>成 (1938) 八月廿九日，外洋汉章寄潮汕母洒大人</t>
+          <t>戊（1938）八月廿九日，外洋汉章寄潮汕母亲大人</t>
         </is>
       </c>
       <c r="E66" s="12" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>十七年 (1938) 十月，退李期周寄馈邑下保李宅张氏荆妻</t>
+          <t>廿七年（1938）十月，暹李期周寄饶邑下堡李宅张氏荆妻</t>
         </is>
       </c>
       <c r="E67" s="12" t="inlineStr">
@@ -3867,7 +3867,7 @@
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>民國二十七年 (1938) 十二月三号，进陈文高寄饶隆前溪陈乡陈宅双亲大人</t>
+          <t>民国二十七年（1938）十二月三号，暹陈文高寄饶隆前溪陈乡陈宅双亲大人</t>
         </is>
       </c>
       <c r="E68" s="12" t="inlineStr">
@@ -3924,7 +3924,7 @@
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>成 (1938) 十月廿四，越丁南寄潮安南桂都姚庆松吾儿</t>
+          <t>戊（1938）十月廿四，越丁南寄潮安南桂都姚庆松吾儿</t>
         </is>
       </c>
       <c r="E69" s="12" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
-          <t>成 (1939) 十一月十七日, 外洋佳銳寄潮汕慈母大人</t>
+          <t>戊（1939）十一月十七日，外洋佳锐寄潮汕慈母大人</t>
         </is>
       </c>
       <c r="E70" s="12" t="inlineStr">
@@ -4034,7 +4034,7 @@
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>填八年 (1939) 正月十三日，号许美硬寄潮安西洋乡张运俊先生</t>
+          <t>廿八年（1939）正月十三日，叻许美馥寄潮安西洋乡张运俊先生</t>
         </is>
       </c>
       <c r="E71" s="12" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>己 (1939) 二月十九日, 肋宋樹到寄澄吧下醫家雙親大人</t>
+          <t>己（1939）二月十九日，叻宋树钊寄澄邑下蓬家双亲大人</t>
         </is>
       </c>
       <c r="E72" s="12" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>己 (1939) 三月初一日, 外洋潘賢偉寄潮安東苗區潘慶絆吾仟</t>
+          <t>己（1939）三月初一日，外洋潘贤伟寄潮安东莆区潘庆奎吾侄</t>
         </is>
       </c>
       <c r="E73" s="12" t="inlineStr">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="D74" s="12" t="inlineStr">
         <is>
-          <t>己 (1939) 三月甘一日，[助]郑万道寄潮安五区家双亲大人</t>
+          <t>己（1939）三月廿一日，［叻］郑万道寄潮安五区家双亲大人</t>
         </is>
       </c>
       <c r="E74" s="12" t="inlineStr">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>己 (1939) 四月初一日，超应杰寄洒 (溢) 邑外埔乡黄应瑜吾弟</t>
+          <t>己（1939）四月初一日，暹应杰寄汀（澄）邑外埔乡黄应瑜吾弟</t>
         </is>
       </c>
       <c r="E75" s="12" t="inlineStr">
@@ -4322,7 +4322,7 @@
       </c>
       <c r="D76" s="12" t="inlineStr">
         <is>
-          <t>己 (1939) 十一月初九日，[号】树钊寄【漆吧下医】笑娇内子</t>
+          <t>己（1939）十一月初九日，［叻］树钊寄［澄邑下蓬］笑娇内子</t>
         </is>
       </c>
       <c r="E76" s="12" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="D77" s="12" t="inlineStr">
         <is>
-          <t>民廿九年 (1940) 二月一日, 泰 [泰國」財福寄澄邑南砂鄉林和宅慈親大人</t>
+          <t>民廿九年（1940）二月一日，泰［泰国］财福寄澄邑南砂乡林宅慈亲大人</t>
         </is>
       </c>
       <c r="E77" s="12" t="inlineStr">
@@ -4430,7 +4430,7 @@
       </c>
       <c r="D78" s="12" t="inlineStr">
         <is>
-          <t>甘九年 (1940) 二月三十日，潮安稚塘乡儿光容寄进陈运异父亲大人</t>
+          <t>廿九年（1940）二月三十日，潮安鹤塘乡儿光裕寄暹陈运昇父亲大人</t>
         </is>
       </c>
       <c r="E78" s="12" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>二十九年 (1940) 三月目九日, 是曾大專寄澄邑中外都家妨母大人</t>
+          <t>二十九年（1940）三月廿九日，暹曾大专寄澄邑中外都家婶母大人</t>
         </is>
       </c>
       <c r="E79" s="12" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="D80" s="12" t="inlineStr">
         <is>
-          <t>庚(1940) 六月初三日，吓陈赞堂寄潮安东风村刘氏荆妻</t>
+          <t>庚（1940）六月初三日，叻陈赞堂寄潮安东凤村刘氏荆妻</t>
         </is>
       </c>
       <c r="E80" s="12" t="inlineStr">
@@ -4599,7 +4599,7 @@
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>康辰年 (1940) 六月初五日，咏郑万道寄潮安五区家双亲大人</t>
+          <t>庚辰年（1940）六月初五日，叻郑万道寄潮安五区家双亲大人</t>
         </is>
       </c>
       <c r="E81" s="12" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="D82" s="12" t="inlineStr">
         <is>
-          <t>二十九年(1940) 阴历七月初十日，外洋曾大专寄潮汕姊母大人</t>
+          <t>二十九年（1940）阴历七月初十日，外洋曾大专寄潮汕姊母大人</t>
         </is>
       </c>
       <c r="E82" s="12" t="inlineStr">
@@ -4707,7 +4707,7 @@
       </c>
       <c r="D83" s="12" t="inlineStr">
         <is>
-          <t>庚 (1940) 七月廿日，号刘祥页寄潮安东风村陈学炎先生</t>
+          <t>庚（1940）七月廿日，叻刘祥贞寄潮安东凤村陈学炎先生</t>
         </is>
       </c>
       <c r="E83" s="12" t="inlineStr">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="D84" s="12" t="inlineStr">
         <is>
-          <t>庚 (1940) 十一月十五日, 號潘兆祥寄饒邑隆都家祖慈大人</t>
+          <t>庚（1940）十一月十五日，叻潘兆祥寄饶邑隆都家祖慈大人</t>
         </is>
       </c>
       <c r="E84" s="12" t="inlineStr">
@@ -4820,7 +4820,7 @@
       </c>
       <c r="D85" s="12" t="inlineStr">
         <is>
-          <t>康辰年 (1940) 十二月初三日，外洋万道寄潮汕双亲大人</t>
+          <t>庚辰年（1940）十一月初三日，外洋万道寄潮汕双亲大人</t>
         </is>
       </c>
       <c r="E85" s="12" t="inlineStr">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="D86" s="12" t="inlineStr">
         <is>
-          <t>卅年 (1941) 一月十七日, 叻尊森綿寄潮安南桂家慈訂大人</t>
+          <t>卅年（1941）一月十七日，叻郑木绵寄潮安南桂家慈亲大人</t>
         </is>
       </c>
       <c r="E86" s="12" t="inlineStr">
@@ -4929,7 +4929,7 @@
       </c>
       <c r="D87" s="12" t="inlineStr">
         <is>
-          <t>辛 (1941) 元月初五日, 叻潘兆祥寄饒邑隆都家祖慈大人</t>
+          <t>辛（1941）元月初五日，叻潘兆祥寄饶邑隆都家祖慈大人</t>
         </is>
       </c>
       <c r="E87" s="12" t="inlineStr">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="D88" s="12" t="inlineStr">
         <is>
-          <t>冊年 (1941) 二月四日, 叻陳照廷寄潮安南桂區陳學炎先生</t>
+          <t>卅年（1941）二月四日，叻陈照廷寄潮安南桂区陈学炎先生</t>
         </is>
       </c>
       <c r="E88" s="12" t="inlineStr">
@@ -5043,7 +5043,7 @@
       </c>
       <c r="D89" s="12" t="inlineStr">
         <is>
-          <t>辛 (1941) 二月廿六日，麻 [马来亚麻坡] 林榮果寄潮安古樓鄉林杰標全</t>
+          <t>辛（1941）二月廿六日，麻［马来亚麻坡］林荣泉寄潮安古楼乡林杰标侄</t>
         </is>
       </c>
       <c r="E89" s="12" t="inlineStr">
@@ -5100,7 +5100,7 @@
       </c>
       <c r="D90" s="12" t="inlineStr">
         <is>
-          <t>辛已年 (1941) 四月初五日,〔叻】 鄭萬道寄〔潮安五區] 雙親大人</t>
+          <t>辛巳年（1941）四月初五日，［叻］郑万道寄［潮安五区］双亲大人</t>
         </is>
       </c>
       <c r="E90" s="12" t="inlineStr">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="D91" s="12" t="inlineStr">
         <is>
-          <t>辛已年 (1941) 七月十八日，助郑万道寄潮安五区家双亲大人</t>
+          <t>辛巳年（1941）七月十八日，叻郑万道寄潮安五区家双亲大人</t>
         </is>
       </c>
       <c r="E91" s="12" t="inlineStr">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="D92" s="12" t="inlineStr">
         <is>
-          <t>痊 (1941) 九月初九日，槟城 [马来亚] 潘兆祥寄饒吧隆都家祖慈大人</t>
+          <t>辛（1941）九月初九日，槟城［马来亚］潘兆祥寄饶邑隆都家祖慈大人</t>
         </is>
       </c>
       <c r="E92" s="12" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="D93" s="12" t="inlineStr">
         <is>
-          <t>辛 (1941) 九月十八日, 外洋潘兆珊寄潮汕家賢妻</t>
+          <t>辛（1941）九月十八日，外洋潘兆珊寄潮汕家贤妻</t>
         </is>
       </c>
       <c r="E93" s="12" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="D94" s="12" t="inlineStr">
         <is>
-          <t>五月十三日 (約1942 前), 外洋繼豪寄潮汕慈親大人</t>
+          <t>五月十三日（约1942前），外洋继豪寄潮汕慈亲大人</t>
         </is>
       </c>
       <c r="E94" s="12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="D95" s="12" t="inlineStr">
         <is>
-          <t>問六月廿八日 (約1942 前) ，外洋有存寄潮汕慈亲大人</t>
+          <t>闰六月廿八日（约1942前），外洋有存寄潮汕慈亲大人</t>
         </is>
       </c>
       <c r="E95" s="12" t="inlineStr">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="D96" s="12" t="inlineStr">
         <is>
-          <t>八月初三日 (約1942 前) ，外洋步潜寄潮汕楷模、楷兴两侄</t>
+          <t>八月初三日（约1942前），外洋步潜寄潮汕楷模、楷钦两侄</t>
         </is>
       </c>
       <c r="E96" s="12" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="D97" s="12" t="inlineStr">
         <is>
-          <t>九月初二日 (約1942 前), 外洋陳孝先寄潮汕姑母大人</t>
+          <t>九月初二日（约1942前），外洋陈孝先寄潮汕姑母大人</t>
         </is>
       </c>
       <c r="E97" s="12" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="D98" s="12" t="inlineStr">
         <is>
-          <t>初三日 (约 1942 前)，进曾君干寄漆色渡头曾炮举之母</t>
+          <t>初三日（约1942前），暹曾君干寄澄邑渡头曾耀举之母</t>
         </is>
       </c>
       <c r="E98" s="12" t="inlineStr">
@@ -5585,7 +5585,7 @@
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>民國冊四年 (1945) 九月廿五叻, 外洋繼豪寄潮汕母親大人</t>
+          <t>民国卅四年（1945）九月廿五号，外洋继豪寄潮汕母亲大人</t>
         </is>
       </c>
       <c r="E99" s="12" t="inlineStr">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="D100" s="12" t="inlineStr">
         <is>
-          <t>民國上靈四年(1945) 阴历十月十三日，外洋陈广臣寄潮汕慈亲大人</t>
+          <t>民国卅四年（1945）阴历十月十三日，外洋陈广臣寄潮汕慈亲大人</t>
         </is>
       </c>
       <c r="E100" s="12" t="inlineStr">
@@ -5691,7 +5691,7 @@
       </c>
       <c r="D101" s="12" t="inlineStr">
         <is>
-          <t>民国州四年(1945) 十一月廿五日，号陈昌凯寄潮安头头乡家母亲大人</t>
+          <t>民国卅四年（1945）十二月廿五日，叻陈昌凯寄潮安鳌头乡家母亲大人</t>
         </is>
       </c>
       <c r="E101" s="12" t="inlineStr">
@@ -5748,7 +5748,7 @@
       </c>
       <c r="D102" s="12" t="inlineStr">
         <is>
-          <t>民國冊五年 (1946) 四月初四日, 外洋陳靜劉寄潮油祝榮嫦</t>
+          <t>民国卅五年（1946）四月初四日，外洋陈静卿寄潮汕祝荣嫦</t>
         </is>
       </c>
       <c r="E102" s="12" t="inlineStr">
@@ -5801,7 +5801,7 @@
       </c>
       <c r="D103" s="12" t="inlineStr">
         <is>
-          <t>才五年 (1946) 七月十三，助方源德寄潮安登云区家源木胞弟</t>
+          <t>卅五年（1946）七月廿三，叻方源德寄潮安登云区家源木胞弟</t>
         </is>
       </c>
       <c r="E103" s="12" t="inlineStr">
@@ -5857,7 +5857,7 @@
       </c>
       <c r="D104" s="12" t="inlineStr">
         <is>
-          <t>民州五年(1946) 八月十二日，新加坡潘睁祥寄饶即括砂乡家慈亲大人</t>
+          <t>民卅五年（1946）八月十二日，新加坡潘兆祥寄饶邑碧砂乡家慈亲大人</t>
         </is>
       </c>
       <c r="E104" s="12" t="inlineStr">
@@ -5914,7 +5914,7 @@
       </c>
       <c r="D105" s="12" t="inlineStr">
         <is>
-          <t>中华民国州五年(1946) 九月吉日, 叻陳逢松寄潮安整頭鄉黃氏吾妻</t>
+          <t>中华民国卅五年（1946）九月卅日，叻陈逢松寄潮安鳌头乡黄氏吾妻</t>
         </is>
       </c>
       <c r="E105" s="12" t="inlineStr">
@@ -5970,7 +5970,7 @@
       </c>
       <c r="D106" s="12" t="inlineStr">
         <is>
-          <t>民冊五年 (1946) 十一月十二日, 新加坡潘兆祥寄饒邑碧砂鄉家慈訂大人</t>
+          <t>民卅五年（1946）十一月十二日，新加坡潘兆祥寄饶邑碧砂乡家慈亲大人</t>
         </is>
       </c>
       <c r="E106" s="12" t="inlineStr">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="D107" s="12" t="inlineStr">
         <is>
-          <t>再成(1946) 十一月十六日, 外洋郭玉風寄潮汕嫂盡</t>
+          <t>丙戌（1946）十一月十六日，外洋郭玉凤寄潮汕嫂嫂</t>
         </is>
       </c>
       <c r="E107" s="12" t="inlineStr">
@@ -6079,7 +6079,7 @@
       </c>
       <c r="D108" s="12" t="inlineStr">
         <is>
-          <t>冊六年 (1947) 四月六日, 四張林和春寄潮安南桂都張宅慈親大人</t>
+          <t>卅六年（1947）四月六日，暹张木春寄潮安南桂都张宅慈亲大人</t>
         </is>
       </c>
       <c r="E108" s="12" t="inlineStr">
@@ -6136,7 +6136,7 @@
       </c>
       <c r="D109" s="12" t="inlineStr">
         <is>
-          <t>丁刻(1947) 四月初十日, 叻林壁書寄潮安南桂張戀書先生</t>
+          <t>丁亥（1947）四月初十日，叻林壁书寄潮安南桂张銮书先生</t>
         </is>
       </c>
       <c r="E109" s="12" t="inlineStr">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="D110" s="12" t="inlineStr">
         <is>
-          <t>本次(1947) 四月目四日, 外洋張文潮寄潮汕慈訂大人</t>
+          <t>丁亥（1947）四月廿四日，外洋张文潮寄潮汕慈亲大人</t>
         </is>
       </c>
       <c r="E110" s="12" t="inlineStr">
@@ -6245,7 +6245,7 @@
       </c>
       <c r="D111" s="12" t="inlineStr">
         <is>
-          <t>冊六年 (1947) 五月九日，巴双 |[马来亚] 陈燕初寄潮安整头乡陈巷城先且</t>
+          <t>卅六年（1947）五月九日，巴双［马来亚］陈燕初寄潮安鳌头乡陈燕城先生</t>
         </is>
       </c>
       <c r="E111" s="12" t="inlineStr">
@@ -6302,7 +6302,7 @@
       </c>
       <c r="D112" s="12" t="inlineStr">
         <is>
-          <t>中华民国州六年(1947) 五月廿九日，号宋迷正寄湾邑下顾宋树昭先生</t>
+          <t>中华民国卅六年（1947）五月廿九日，叻宋耀正寄澄邑下蓬宋树昭先生</t>
         </is>
       </c>
       <c r="E112" s="12" t="inlineStr">
@@ -6359,7 +6359,7 @@
       </c>
       <c r="D113" s="12" t="inlineStr">
         <is>
-          <t>丁 (1947) 七月初十日, 柔佛 [马来亚] 李再网弟寄潮安臣集乡李再赐胞兄</t>
+          <t>丁（1947）七月初十日，柔佛［马来亚］李再赐弟寄潮安鹤巢乡李再赐胞兄</t>
         </is>
       </c>
       <c r="E113" s="12" t="inlineStr">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="D114" s="12" t="inlineStr">
         <is>
-          <t>丁 (1947) 七月十四日，潮安江东母寄泰国张得惜吾儿</t>
+          <t>丁（1947）七月十四日，潮安江东母寄泰国张得惜吾儿</t>
         </is>
       </c>
       <c r="E114" s="12" t="inlineStr">
@@ -6467,7 +6467,7 @@
       </c>
       <c r="D115" s="12" t="inlineStr">
         <is>
-          <t>丁亦(1947) 八月初四日, 號張文潮寄潮安南桂鄉家慈親大人</t>
+          <t>丁亥（1947）八月初四日，叻张文潮寄潮安南桂乡家慈亲大人</t>
         </is>
       </c>
       <c r="E115" s="12" t="inlineStr">
@@ -6523,7 +6523,7 @@
       </c>
       <c r="D116" s="12" t="inlineStr">
         <is>
-          <t>冊六年 (1947) 十月八日, 叻名四峇寄潮安登隆都劉捷鎮先生</t>
+          <t>卅六年（1947）十月八日，叻刘四合寄潮安登隆都刘捷镇先生</t>
         </is>
       </c>
       <c r="E116" s="12" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="D117" s="12" t="inlineStr">
         <is>
-          <t>丁刻年(1947) 十月廿七日, 外洋致祥寄潮汕表嫂</t>
+          <t>丁亥年（1947）十月廿七日，外洋致祥寄潮汕表嫂</t>
         </is>
       </c>
       <c r="E117" s="12" t="inlineStr">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="D118" s="12" t="inlineStr">
         <is>
-          <t>冊六年 (1947) 阴十一月初四日，外洋广臣宕潮汕素亲大人</t>
+          <t>卅六年（1947）阴十一月初四日，外洋广臣寄潮汕慈亲大人</t>
         </is>
       </c>
       <c r="E118" s="12" t="inlineStr">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="D119" s="12" t="inlineStr">
         <is>
-          <t>靈六年 (1947) 十二月初三日，外洋父寄潮汕茂鉴吾儿</t>
+          <t>卅六年（1947）十二月初三日，外洋父寄潮汕茂鉴吾儿</t>
         </is>
       </c>
       <c r="E119" s="12" t="inlineStr">
@@ -6749,7 +6749,7 @@
       </c>
       <c r="D120" s="12" t="inlineStr">
         <is>
-          <t>丁 (1948) 完月(十二月) 初十日，外洋沈波南寄潮汕岳母大人</t>
+          <t>丁（1948）完月（十二月）初十日，外洋沈波南寄潮汕岳母大人</t>
         </is>
       </c>
       <c r="E120" s="12" t="inlineStr">
@@ -6803,7 +6803,7 @@
       </c>
       <c r="D121" s="12" t="inlineStr">
         <is>
-          <t>州七年 (1948) 元月一十八日, 港 [香港] 李楞枝寄潮安南桂家双亲大人</t>
+          <t>卅七年（1948）元月二十八日，港［香港］李楞枝寄潮安南桂家双亲大人</t>
         </is>
       </c>
       <c r="E121" s="12" t="inlineStr">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="D122" s="12" t="inlineStr">
         <is>
-          <t>靈七年 (1948) 二月七日，进张木春寄潮安南柱都张宅慈亲大人</t>
+          <t>卅七年（1948）二月七日，暹张木春寄潮安南桂都张宅慈亲大人</t>
         </is>
       </c>
       <c r="E122" s="12" t="inlineStr">
@@ -6916,7 +6916,7 @@
       </c>
       <c r="D123" s="12" t="inlineStr">
         <is>
-          <t>民國靈七年 (1948) 三月廿五，[助]陈着松寄【 潮安整头乡]黄氏吾妻</t>
+          <t>民国卅七年（1948）三月廿五，［叻］陈逢松寄［潮安鳌头乡］黄氏吾妻</t>
         </is>
       </c>
       <c r="E123" s="12" t="inlineStr">
@@ -6969,7 +6969,7 @@
       </c>
       <c r="D124" s="12" t="inlineStr">
         <is>
-          <t>民國靈七年 (1948) 四月十一日, !叻陳逢松寄潮安整頭鄉黃氏吾妻</t>
+          <t>民国卅七年（1948）四月廿一日，叻陈逢松寄潮安鳌头乡黄氏吾妻</t>
         </is>
       </c>
       <c r="E124" s="12" t="inlineStr">
@@ -7026,7 +7026,7 @@
       </c>
       <c r="D125" s="12" t="inlineStr">
         <is>
-          <t>戊子年 (1948) 五月廿五日, 外洋忠秋寄潮汕慈訂大人</t>
+          <t>戊子年（1948）五月廿五日，外洋毓秋寄潮汕慈亲大人</t>
         </is>
       </c>
       <c r="E125" s="12" t="inlineStr">
@@ -7079,7 +7079,7 @@
       </c>
       <c r="D126" s="12" t="inlineStr">
         <is>
-          <t>一九四八年, 砂拉越張澤盛寄潮安第五區張倫勤</t>
+          <t>一九四八年，砂拉越张泽盛寄潮安第五区张叙勤</t>
         </is>
       </c>
       <c r="E126" s="12" t="inlineStr">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="D127" s="12" t="inlineStr">
         <is>
-          <t>四月初九日 (約1949 前), 外洋母寄潮汕金祥吾兒</t>
+          <t>四月初九日（约1949前），外洋母寄潮汕金祥吾儿</t>
         </is>
       </c>
       <c r="E127" s="12" t="inlineStr">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="D128" s="12" t="inlineStr">
         <is>
-          <t>四月十九日 (約1949 前), 越張永金寄潮安南桂區慈訂大人</t>
+          <t>四月十九日（约1949前），越张永金寄潮安南桂区慈亲大人</t>
         </is>
       </c>
       <c r="E128" s="12" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="D129" s="12" t="inlineStr">
         <is>
-          <t>八月十七日 (約1949 前), 麻坡鄭容潮寄潮安南桂鄉家慈訂大人</t>
+          <t>八月十七日（约1949前），麻坡郑裕潮寄潮安南桂乡家慈亲大人</t>
         </is>
       </c>
       <c r="E129" s="12" t="inlineStr">
@@ -7309,7 +7309,7 @@
       </c>
       <c r="D130" s="12" t="inlineStr">
         <is>
-          <t>八月甘一日 (約1949 前), 叻老妨寄澄吧下轎宋樹到賢倒</t>
+          <t>八月廿一日（约1949前），叻老妨寄澄邑下蓬宋树钊贤侄</t>
         </is>
       </c>
       <c r="E130" s="12" t="inlineStr">
@@ -7365,7 +7365,7 @@
       </c>
       <c r="D131" s="12" t="inlineStr">
         <is>
-          <t>十月甘日 (約1949 前), 號宋樹到寄汀(澄) 邑下鞍家双亲大人</t>
+          <t>十月廿日（约1949前），叻宋树钊寄汀（澄）邑下蓬家双亲大人</t>
         </is>
       </c>
       <c r="E131" s="12" t="inlineStr">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="D132" s="12" t="inlineStr">
         <is>
-          <t>成 (1948) 八月廿一日，号陈捷倒寄潮安整头陈世上昭长男</t>
+          <t>戊（1948）八月廿一日，叻陈捷钦寄潮安鳌头陈世昭长男</t>
         </is>
       </c>
       <c r="E132" s="12" t="inlineStr">
@@ -7480,7 +7480,7 @@
       </c>
       <c r="D133" s="12" t="inlineStr">
         <is>
-          <t>九月廿八日 (1948) , 越張永金寄潮安南桂區慈親大人</t>
+          <t>九月廿八日（1948），越张永金寄潮安南桂区慈亲大人</t>
         </is>
       </c>
       <c r="E133" s="12" t="inlineStr">
@@ -7536,7 +7536,7 @@
       </c>
       <c r="D134" s="12" t="inlineStr">
         <is>
-          <t>中华民国州七年(1948) 十一月初一日, 肋楊森良寄汕頭市新馬路楊子忠先同</t>
+          <t>中华民国卅七年（1948）十一月初一日，叻杨木良寄汕头市新马路杨子忠先生</t>
         </is>
       </c>
       <c r="E134" s="12" t="inlineStr">
@@ -7593,7 +7593,7 @@
       </c>
       <c r="D135" s="12" t="inlineStr">
         <is>
-          <t>一九四八年, 叻鄭奕玉寄潮安南桂家慈座大人</t>
+          <t>一九四八年，叻郑奕玉寄潮安南桂家慈亲大人</t>
         </is>
       </c>
       <c r="E135" s="12" t="inlineStr">
@@ -7650,7 +7650,7 @@
       </c>
       <c r="D136" s="12" t="inlineStr">
         <is>
-          <t>民国州八年(1949) 元月初七日，外洋炳极寄潮汕苹亲大人</t>
+          <t>民国卅八年（1949）元月初七日，外洋炳极寄潮汕母亲大人</t>
         </is>
       </c>
       <c r="E136" s="12" t="inlineStr">
@@ -7703,7 +7703,7 @@
       </c>
       <c r="D137" s="12" t="inlineStr">
         <is>
-          <t>靈八年 (1949) 一月十二日, 號張運俊寄潮安南桂張孟到先生</t>
+          <t>卅八年（1949）一月十二日，叻张运俊寄潮安南桂张孟钊先生</t>
         </is>
       </c>
       <c r="E137" s="12" t="inlineStr">
@@ -7760,7 +7760,7 @@
       </c>
       <c r="D138" s="12" t="inlineStr">
         <is>
-          <t>民域八年 (1949) 元月十七, 肋吳坤豐寄潮安銀湖村許氏州妻</t>
+          <t>民卅八年（1949）元月十七，叻吴坤丰寄潮安银湖村许氏荆妻</t>
         </is>
       </c>
       <c r="E138" s="12" t="inlineStr">
@@ -7816,7 +7816,7 @@
       </c>
       <c r="D139" s="12" t="inlineStr">
         <is>
-          <t>一月十四日 (1949) ，外洋黄居禧寄潮汕岳母大人</t>
+          <t>二月十四日（1949），外洋黄居禧寄潮汕岳母大人</t>
         </is>
       </c>
       <c r="E139" s="12" t="inlineStr">
@@ -7868,7 +7868,7 @@
       </c>
       <c r="D140" s="12" t="inlineStr">
         <is>
-          <t>中华民国州八年 (1949) 四月十八日, 外洋梅寄潮汕母親大人</t>
+          <t>中华民国卅八年（1949）四月十八日，外洋梅寄潮汕母亲大人</t>
         </is>
       </c>
       <c r="E140" s="12" t="inlineStr">
@@ -7922,7 +7922,7 @@
       </c>
       <c r="D141" s="12" t="inlineStr">
         <is>
-          <t>己 (1949) 六月初七日，外洋长丰寄潮汕继豪族倒台</t>
+          <t>己（1949）六月初七日，外洋长丰寄潮汕继豪族侄台</t>
         </is>
       </c>
       <c r="E141" s="12" t="inlineStr">
@@ -7974,7 +7974,7 @@
       </c>
       <c r="D142" s="12" t="inlineStr">
         <is>
-          <t>民國三十八年 (1949) 八月初二日, 外洋尊萬豪寄潮汕慈親大人</t>
+          <t>民国三十八年（1949）八月初二日，外洋郑万豪寄潮汕慈亲大人</t>
         </is>
       </c>
       <c r="E142" s="12" t="inlineStr">
@@ -8026,7 +8026,7 @@
       </c>
       <c r="D143" s="12" t="inlineStr">
         <is>
-          <t>民卅八年 (1949) 八月三日，外洋陈享发寄潮汕朝居宗倒台</t>
+          <t>民卅八年（1949）八月三日，外洋陈亨发寄潮汕朝居宗侄台</t>
         </is>
       </c>
       <c r="E143" s="12" t="inlineStr">
@@ -8078,7 +8078,7 @@
       </c>
       <c r="D144" s="12" t="inlineStr">
         <is>
-          <t>旧历图七月初九日、九月一号(1949) ，外洋郑炳存、郑惠英寄潮汕细姨母大人</t>
+          <t>旧历闰七月初九日、九月一号（1949），外洋郑炳存、郑惠英寄潮汕细姨母大人</t>
         </is>
       </c>
       <c r="E144" s="12" t="inlineStr">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="D145" s="12" t="inlineStr">
         <is>
-          <t>九月十日(民国) ，外洋省斌寄潮汕克能全</t>
+          <t>九月十日（民国），外洋省斌寄潮汕克能侄</t>
         </is>
       </c>
       <c r="E145" s="12" t="inlineStr">
@@ -8184,7 +8184,7 @@
       </c>
       <c r="D146" s="12" t="inlineStr">
         <is>
-          <t>(民国) 外洋曉澄寄潮汕大恕(姊)</t>
+          <t>（民国）外洋晓澄寄潮汕大姆（姊）</t>
         </is>
       </c>
       <c r="E146" s="12" t="inlineStr">
@@ -8240,7 +8240,7 @@
       </c>
       <c r="D147" s="12" t="inlineStr">
         <is>
-          <t>庚寅年 (1950) 元月初九日，外洋父寄潮汕茂鉴吾儿</t>
+          <t>庚寅年（1950）元月初九日，外洋父寄潮汕茂鉴吾儿</t>
         </is>
       </c>
       <c r="E147" s="12" t="inlineStr">
@@ -8292,7 +8292,7 @@
       </c>
       <c r="D148" s="12" t="inlineStr">
         <is>
-          <t>一九五OO年元月州日，号强兴寄潮安南桂张君远吾儿</t>
+          <t>一九五○年元月廿日，叻强兴寄潮安南桂张君远吾儿</t>
         </is>
       </c>
       <c r="E148" s="12" t="inlineStr">
@@ -8349,7 +8349,7 @@
       </c>
       <c r="D149" s="12" t="inlineStr">
         <is>
-          <t>庚賓 (1950) 三月初九日，外洋父寄潮汕臣鉴吾儿</t>
+          <t>庚寅（1950）三月初九日，外洋父寄潮汕茂鉴吾儿</t>
         </is>
       </c>
       <c r="E149" s="12" t="inlineStr">
@@ -8402,7 +8402,7 @@
       </c>
       <c r="D150" s="12" t="inlineStr">
         <is>
-          <t>阴历四月初十日 (1950) ，麻坡郑浴潮寄潮安南桂乡家慈亲大人</t>
+          <t>阴历四月初七日（1950），麻坡郑裕潮寄潮安南桂乡家慈亲大人</t>
         </is>
       </c>
       <c r="E150" s="12" t="inlineStr">
@@ -8462,7 +8462,7 @@
       </c>
       <c r="D151" s="12" t="inlineStr">
         <is>
-          <t>六月初六日、七月廿日 (1950)，助宋树蚀寄溢邑下蓝英弟</t>
+          <t>六月初六日、七月廿日（1950），叻宋树钊寄澄邑下蓬英弟</t>
         </is>
       </c>
       <c r="E151" s="12" t="inlineStr">
@@ -8519,7 +8519,7 @@
       </c>
       <c r="D152" s="12" t="inlineStr">
         <is>
-          <t>(約1950) 〔叻宋樹歸] 寄〔澄吧下轎】英弟</t>
+          <t>（约1950）［叻宋树钊］寄［澄邑下蓬］英弟</t>
         </is>
       </c>
       <c r="E152" s="12" t="inlineStr">
@@ -8582,7 +8582,7 @@
       </c>
       <c r="D153" s="12" t="inlineStr">
         <is>
-          <t>六月十一日 (1950) , 功廖仕補寄潮安大寨家慈親大人</t>
+          <t>六月十一日（1950），叻廖仕禄寄潮安大寨家慈亲大人</t>
         </is>
       </c>
       <c r="E153" s="12" t="inlineStr">
@@ -8639,7 +8639,7 @@
       </c>
       <c r="D154" s="12" t="inlineStr">
         <is>
-          <t>阴历七月廿六日 (1950) , 麻坡尊容潮寄潮安縣南桂鄉家慈親大人</t>
+          <t>阴历七月廿六日（1950），麻坡郑裕潮寄潮安县南桂乡家慈亲大人</t>
         </is>
       </c>
       <c r="E154" s="12" t="inlineStr">
@@ -8700,7 +8700,7 @@
       </c>
       <c r="D155" s="12" t="inlineStr">
         <is>
-          <t>庚年(1950) 十一月初四日，外洋黄居禧寄潮汕岳母大人</t>
+          <t>庚年（1950）十一月初四日，外洋黄居禧寄潮汕岳母大人</t>
         </is>
       </c>
       <c r="E155" s="12" t="inlineStr">
@@ -8757,7 +8757,7 @@
       </c>
       <c r="D156" s="12" t="inlineStr">
         <is>
-          <t>庚年 (1950) 十一月初八日, 外洋姆寄潮汕一妨</t>
+          <t>庚年（1950）十一月初八日，外洋姆寄潮汕二婶</t>
         </is>
       </c>
       <c r="E156" s="12" t="inlineStr">
@@ -8810,7 +8810,7 @@
       </c>
       <c r="D157" s="12" t="inlineStr">
         <is>
-          <t>庚 (1951) 十一月初九日, 柔佛吳正標寄潮安攀昌鄉李再賜先生</t>
+          <t>庚（1951）十二月初九日，柔佛吴正标寄潮安鹤巢乡李再赐先生</t>
         </is>
       </c>
       <c r="E157" s="12" t="inlineStr">
@@ -8867,7 +8867,7 @@
       </c>
       <c r="D158" s="12" t="inlineStr">
         <is>
-          <t>三月十二日、二月初五日 (1951)，吓宋树蚀寄洒 (洪) 邑下偿家花灯大人</t>
+          <t>三月十二日、二月初五日（1951），叻宋树钊寄汀（澄）邑下蓬家慈亲大人</t>
         </is>
       </c>
       <c r="E158" s="12" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="D159" s="12" t="inlineStr">
         <is>
-          <t>一九五一四月六日，外洋宝果寄潮汕戊谦兄</t>
+          <t>一九五一四月六日，外洋宝泉寄潮汕戊谦兄</t>
         </is>
       </c>
       <c r="E159" s="12" t="inlineStr">
@@ -8978,7 +8978,7 @@
       </c>
       <c r="D160" s="12" t="inlineStr">
         <is>
-          <t>辛 (1951) 五月初三日，外洋强兴寄潮汕御婴贤妻</t>
+          <t>辛（1951）五月初三日，外洋强兴寄潮汕御卿贤妻</t>
         </is>
       </c>
       <c r="E160" s="12" t="inlineStr">
@@ -9032,7 +9032,7 @@
       </c>
       <c r="D161" s="12" t="inlineStr">
         <is>
-          <t>辛 (1952) 十二月十九日，香高永绵寄漆海县上华区高永豆先生</t>
+          <t>辛（1952）十二月十九日，香港永绵寄澄海县上华区高永彭先生</t>
         </is>
       </c>
       <c r="E161" s="12" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="D162" s="12" t="inlineStr">
         <is>
-          <t>壬 (1952) 六月十五日, 星 [|新加坡] 宋壁初寄湾邑樟林宋南梅先生</t>
+          <t>壬（1952）六月十五日，星［新加坡］宋璧初寄澄邑樟林宋南梅先生</t>
         </is>
       </c>
       <c r="E162" s="12" t="inlineStr">
@@ -9146,7 +9146,7 @@
       </c>
       <c r="D163" s="12" t="inlineStr">
         <is>
-          <t>一九五三年元月十八日, 叻坡陳鏡海寄潮汕妙姿姻姊、家國姻弟</t>
+          <t>一九五三年元月廿八日，叻坡陈镜梅寄潮汕妙姿姻姊、家国姻弟</t>
         </is>
       </c>
       <c r="E163" s="12" t="inlineStr">
@@ -9199,7 +9199,7 @@
       </c>
       <c r="D164" s="12" t="inlineStr">
         <is>
-          <t>傾 (1953) 三月初七日, 越姚丁南寄潮安南桂區家慈親大人</t>
+          <t>癸（1953）三月初七日，越姚丁南寄潮安南桂区家慈亲大人</t>
         </is>
       </c>
       <c r="E164" s="12" t="inlineStr">
@@ -9256,7 +9256,7 @@
       </c>
       <c r="D165" s="12" t="inlineStr">
         <is>
-          <t>一九五三年三月初九日, 號坡陳鏡海寄潮汕家國姻弟、妙姿姻姊</t>
+          <t>一九五三年三月初九日，叻坡陈镜梅寄潮汕家国姻弟、妙姿姻姊</t>
         </is>
       </c>
       <c r="E165" s="12" t="inlineStr">
@@ -9308,7 +9308,7 @@
       </c>
       <c r="D166" s="12" t="inlineStr">
         <is>
-          <t>一九五三年十二月廿九日，外洋攀河寄潮汕慈兴大人</t>
+          <t>一九五三年十二月廿九日，外洋攀河寄潮汕慈亲大人</t>
         </is>
       </c>
       <c r="E166" s="12" t="inlineStr">
@@ -9361,7 +9361,7 @@
       </c>
       <c r="D167" s="12" t="inlineStr">
         <is>
-          <t>一九五四年元月十五日，号陈祥兰寄潮安秋溪陈炎梅先生</t>
+          <t>一九五四年元月十五日，叻陈祥兰寄潮安秋溪陈炎梅先生</t>
         </is>
       </c>
       <c r="E167" s="12" t="inlineStr">
@@ -9417,7 +9417,7 @@
       </c>
       <c r="D168" s="12" t="inlineStr">
         <is>
-          <t>一九五四年二月初六日, 號廖仕打寄潮安第七區家慈床大人</t>
+          <t>一九五四年二月初六日，叻廖仕泉寄潮安第七区家慈亲大人</t>
         </is>
       </c>
       <c r="E168" s="12" t="inlineStr">
@@ -9474,7 +9474,7 @@
       </c>
       <c r="D169" s="12" t="inlineStr">
         <is>
-          <t>一九五四年十一月十日，助张辊兴寄潮安西洋乡张君远吾儿</t>
+          <t>一九五四年十一月十日，叻张乾兴寄潮安西洋乡张君远吾儿</t>
         </is>
       </c>
       <c r="E169" s="12" t="inlineStr">
@@ -9531,7 +9531,7 @@
       </c>
       <c r="D170" s="12" t="inlineStr">
         <is>
-          <t>旧完月(十二月) 十八日 (1955 ) ，外洋锦邓寄潮汕饥娥吾姊;</t>
+          <t>旧完月（十二月）十八日（1955），外洋锦邓寄潮汕锦娥吾姊；甲午年（1955）完月（十二月）十八日，外洋瑞香寄潮汕姑母大人</t>
         </is>
       </c>
       <c r="E170" s="12" t="inlineStr">
@@ -9589,7 +9589,7 @@
       </c>
       <c r="D171" s="12" t="inlineStr">
         <is>
-          <t>55 年5月1日, 外洋木輝寄潮汕慈親大人</t>
+          <t>55年5月1日，外洋木辉寄潮汕慈亲大人</t>
         </is>
       </c>
       <c r="E171" s="12" t="inlineStr">
@@ -9748,7 +9748,7 @@
       </c>
       <c r="D174" s="12" t="inlineStr">
         <is>
-          <t>一九五六年两申四月廿八日，助谢琴音寄潮安观人巢乡李再则先生</t>
+          <t>一九五六年丙申四月廿八日，叻谢琴音寄潮安鹤巢乡李再赐先生</t>
         </is>
       </c>
       <c r="E174" s="12" t="inlineStr">
@@ -9805,7 +9805,7 @@
       </c>
       <c r="D175" s="12" t="inlineStr">
         <is>
-          <t>1957 年7 月 28 日，外洋正贤、逆心寄潮溃后母大人</t>
+          <t>1957年7月28日，外洋正贤、遂心寄潮汕岳母大人</t>
         </is>
       </c>
       <c r="E175" s="12" t="inlineStr">
@@ -9858,7 +9858,7 @@
       </c>
       <c r="D176" s="12" t="inlineStr">
         <is>
-          <t>一九五七年，号郑奕江寄汕头华侨中学校郑万里吾儿</t>
+          <t>一九五七年，叻郑奕江寄汕头华侨中学校郑万里吾儿</t>
         </is>
       </c>
       <c r="E176" s="12" t="inlineStr">
@@ -9968,7 +9968,7 @@
       </c>
       <c r="D178" s="12" t="inlineStr">
         <is>
-          <t>一九五八年十月十四日，外洋杰民寄潮汕压氏吾妻</t>
+          <t>一九五八年十月十四日，外洋杰民寄潮汕丘氏吾妻</t>
         </is>
       </c>
       <c r="E178" s="12" t="inlineStr">
@@ -10074,7 +10074,7 @@
       </c>
       <c r="D180" s="12" t="inlineStr">
         <is>
-          <t>己 (1959) 三月甘九日，助张旭秋寄潮安南桂郑淑坚先生</t>
+          <t>己（1959）三月廿九日，叻张旭秋寄潮安南桂郑淑坚先生</t>
         </is>
       </c>
       <c r="E180" s="12" t="inlineStr">
@@ -10131,7 +10131,7 @@
       </c>
       <c r="D181" s="12" t="inlineStr">
         <is>
-          <t>千寅年 (1962) 八月十八日, 功成子梅寄潮汕慈座大人</t>
+          <t>壬寅年（1962）八月十八日，叻成子梅寄潮汕慈座大人</t>
         </is>
       </c>
       <c r="E181" s="12" t="inlineStr">
@@ -10185,7 +10185,7 @@
       </c>
       <c r="D182" s="12" t="inlineStr">
         <is>
-          <t>一九六三年十一月廿二日，进罗 [泰国] 許金乾寄汀(澄) 樟藉鄉母親</t>
+          <t>一九六三年十一月廿二日，暹罗［泰国］许金乾寄汀（澄）樟籍乡母亲</t>
         </is>
       </c>
       <c r="E182" s="12" t="inlineStr">
@@ -10242,7 +10242,7 @@
       </c>
       <c r="D183" s="12" t="inlineStr">
         <is>
-          <t>一九六四年五月十三日，陈其后寄潮安整头洋东乡母亲大人</t>
+          <t>一九六四年五月十三日，陈其岳寄潮安鳌头洋东乡母亲大人</t>
         </is>
       </c>
       <c r="E183" s="12" t="inlineStr">
@@ -10299,7 +10299,7 @@
       </c>
       <c r="D184" s="12" t="inlineStr">
         <is>
-          <t>甲辰年 (1964) 十一月十一日，助陈捷树寄潮安整头沈亚咀荆妻</t>
+          <t>甲辰年（1964）十一月十一日，叻陈捷树寄潮安鳌头沈亚媛荆妻</t>
         </is>
       </c>
       <c r="E184" s="12" t="inlineStr">
@@ -10409,7 +10409,7 @@
       </c>
       <c r="D186" s="12" t="inlineStr">
         <is>
-          <t>一九六六年十月十二日，号陈玩矫寄潮安整头乡陈广标先生</t>
+          <t>一九六六年十月十二日，叻陈玩侨寄潮安鳌头乡陈广标先生</t>
         </is>
       </c>
       <c r="E186" s="12" t="inlineStr">
@@ -10466,7 +10466,7 @@
       </c>
       <c r="D187" s="12" t="inlineStr">
         <is>
-          <t>1967 年5 月 12 日, 馬來亞鄭容潮寄潮安縣東風鄉家慈訂大人</t>
+          <t>1967年5月12日，马来亚郑裕潮寄潮安县东凤乡家慈亲大人</t>
         </is>
       </c>
       <c r="E187" s="12" t="inlineStr">
@@ -10524,7 +10524,7 @@
       </c>
       <c r="D188" s="12" t="inlineStr">
         <is>
-          <t>一九六八年九月八日, 外洋振海寄潮汕外祖父母大人</t>
+          <t>一九六八年九月八日，外洋振海寄潮汕外祖父母大人</t>
         </is>
       </c>
       <c r="E188" s="12" t="inlineStr">
@@ -10576,7 +10576,7 @@
       </c>
       <c r="D189" s="12" t="inlineStr">
         <is>
-          <t>1972 年1 月25 日，泰国黄缠发寄潮安秋溪都陈贤进姻兄</t>
+          <t>1972年1月25日，泰国黄璋发寄潮安秋溪都陈贤进姻兄</t>
         </is>
       </c>
       <c r="E189" s="12" t="inlineStr">
@@ -10632,7 +10632,7 @@
       </c>
       <c r="D190" s="12" t="inlineStr">
         <is>
-          <t>一九七三年八月廿九日, 外洋藍松江寄潮汕紹浩兄台</t>
+          <t>一九七三年八月廿九日，外洋蓝松江寄潮汕绍浩兄台</t>
         </is>
       </c>
       <c r="E190" s="12" t="inlineStr">
@@ -10685,7 +10685,7 @@
       </c>
       <c r="D191" s="12" t="inlineStr">
         <is>
-          <t>一九八五年元月廿一日，外洋邢树庚、陈婵珠寄潮汕后双亲大人</t>
+          <t>一九八五年元月廿一日，外洋邢树熙、陈婵珠寄潮汕岳双亲大人</t>
         </is>
       </c>
       <c r="E191" s="12" t="inlineStr">
@@ -10741,7 +10741,7 @@
       </c>
       <c r="D192" s="12" t="inlineStr">
         <is>
-          <t>己七月初二日 (1949 后) ，外洋英锋寄潮汕母亲大人</t>
+          <t>己七月初二日（1949后），外洋英锋寄潮汕母亲大人</t>
         </is>
       </c>
       <c r="E192" s="12" t="inlineStr">
@@ -10793,7 +10793,7 @@
       </c>
       <c r="D193" s="12" t="inlineStr">
         <is>
-          <t>庚九月州日 (1949 后) ，外洋永河寄潮汕佩帘吾妻</t>
+          <t>庚九月廿日（1949后），外洋永河寄潮汕佩莺吾妻</t>
         </is>
       </c>
       <c r="E193" s="12" t="inlineStr">
@@ -10845,7 +10845,7 @@
       </c>
       <c r="D194" s="12" t="inlineStr">
         <is>
-          <t>庚十一月初六(1949 後), 外洋孝夠寄潮汕賽蘭吾妻</t>
+          <t>庚十一月初六（1949后），外洋孝钦寄潮汕赛兰吾妻</t>
         </is>
       </c>
       <c r="E194" s="12" t="inlineStr">
@@ -10898,7 +10898,7 @@
       </c>
       <c r="D195" s="12" t="inlineStr">
         <is>
-          <t>辛八月十日 (1949 後), 號部思照寄潮安大黃坑家慈親大人</t>
+          <t>辛八月廿日（1949后），叻郭思照寄潮安大黄坑家慈亲大人</t>
         </is>
       </c>
       <c r="E195" s="12" t="inlineStr">
@@ -10955,7 +10955,7 @@
       </c>
       <c r="D196" s="12" t="inlineStr">
         <is>
-          <t>农元月初八日 (1949 後) , 外洋正賢、遂切寄潮汕岳母大人</t>
+          <t>农元月初八日（1949后），外洋正贤、遂蕊寄潮汕岳母大人</t>
         </is>
       </c>
       <c r="E196" s="12" t="inlineStr">
@@ -11008,7 +11008,7 @@
       </c>
       <c r="D197" s="12" t="inlineStr">
         <is>
-          <t>元月十四日 (1949 后) ，号郑壁硅寄潮安南杜家慈亲大人</t>
+          <t>元月廿四日（1949后），叻郑壁奎寄潮安南桂家慈亲大人</t>
         </is>
       </c>
       <c r="E197" s="12" t="inlineStr">
@@ -11064,7 +11064,7 @@
       </c>
       <c r="D198" s="12" t="inlineStr">
         <is>
-          <t>二-月初四日 (1949 後), 麻坡鄭容潮寄潮安第五區家慈訂大人</t>
+          <t>二月初四日（1949后），麻坡郑裕潮寄潮安第五区家慈亲大人</t>
         </is>
       </c>
       <c r="E198" s="12" t="inlineStr">
@@ -11123,7 +11123,7 @@
       </c>
       <c r="D199" s="12" t="inlineStr">
         <is>
-          <t>二月十七日 (1949 后)，号张居兴寄潮安南桂张牛御侄儿</t>
+          <t>二月十七日（1949后），叻张居兴寄潮安南桂张牛牡侄儿</t>
         </is>
       </c>
       <c r="E199" s="12" t="inlineStr">
@@ -11179,7 +11179,7 @@
       </c>
       <c r="D200" s="12" t="inlineStr">
         <is>
-          <t>四月初四 (1949 后) ，外洋丁陈氏寄潮汕家姑大人</t>
+          <t>四月初四（1949后），外洋丁陈氏寄潮汕家姑大人</t>
         </is>
       </c>
       <c r="E200" s="12" t="inlineStr">
@@ -11233,7 +11233,7 @@
       </c>
       <c r="D201" s="12" t="inlineStr">
         <is>
-          <t>四月七日 (1949 後), 外洋父寄潮汕利仙、英仙女兒</t>
+          <t>四月七日（1949后），外洋父寄潮汕利仙、英仙女儿</t>
         </is>
       </c>
       <c r="E201" s="12" t="inlineStr">
@@ -11287,7 +11287,7 @@
       </c>
       <c r="D202" s="12" t="inlineStr">
         <is>
-          <t>五月初二日 (1949 后) ，外洋张运俊寄潮汕绍娟内助</t>
+          <t>五月初二日（1949后），外洋张运俊寄潮汕绍娟内助</t>
         </is>
       </c>
       <c r="E202" s="12" t="inlineStr">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="D203" s="12" t="inlineStr">
         <is>
-          <t>五月廿五日 (1949 后) ，外洋杨秀兰寄潮汕楚鸿吾儿</t>
+          <t>五月廿五日（1949后），外洋杨秀兰寄潮汕楚鸿吾儿</t>
         </is>
       </c>
       <c r="E203" s="12" t="inlineStr">
@@ -11392,7 +11392,7 @@
       </c>
       <c r="D204" s="12" t="inlineStr">
         <is>
-          <t>五月廿九日 (1949 后) ，外洋丁陈氏寄潮汕家姑大人</t>
+          <t>五月廿九日（1949后），外洋丁陈氏寄潮汕家姑大人</t>
         </is>
       </c>
       <c r="E204" s="12" t="inlineStr">
@@ -11446,7 +11446,7 @@
       </c>
       <c r="D205" s="12" t="inlineStr">
         <is>
-          <t>農歷五月十九日 (1949 后) ，外洋父寄潮汕度鉴儿</t>
+          <t>农历五月廿九日（1949后），外洋父寄潮汕茂鉴儿</t>
         </is>
       </c>
       <c r="E205" s="12" t="inlineStr">
@@ -11498,7 +11498,7 @@
       </c>
       <c r="D206" s="12" t="inlineStr">
         <is>
-          <t>六月初六日 (1949 後), 外洋繼豪寄潮汕潛基仟兒</t>
+          <t>六月初六日（1949后），外洋继豪寄潮汕浩基侄儿</t>
         </is>
       </c>
       <c r="E206" s="12" t="inlineStr">
@@ -11550,7 +11550,7 @@
       </c>
       <c r="D207" s="12" t="inlineStr">
         <is>
-          <t>六月廿七日 (1949 后)，助杨秀苦寄潮安东风乡陈楚鸿吾儿</t>
+          <t>六月廿七日（1949后），叻杨秀兰寄潮安东凤乡陈楚鸿吾儿</t>
         </is>
       </c>
       <c r="E207" s="12" t="inlineStr">
@@ -11607,7 +11607,7 @@
       </c>
       <c r="D208" s="12" t="inlineStr">
         <is>
-          <t>七月十三日 (1949 后) ，外洋永绵寄潮汕母杀大人</t>
+          <t>七月十三日（1949后），外洋永绵寄潮汕母亲大人</t>
         </is>
       </c>
       <c r="E208" s="12" t="inlineStr">
@@ -11660,7 +11660,7 @@
       </c>
       <c r="D209" s="12" t="inlineStr">
         <is>
-          <t>八月十日 (1949 後), 功陳百心寄澄叫隆都活舜良女婚</t>
+          <t>八月廿日（1949后），叻陈碧心寄澄邑隆都潘舜良女儿</t>
         </is>
       </c>
       <c r="E209" s="12" t="inlineStr">
@@ -11717,7 +11717,7 @@
       </c>
       <c r="D210" s="12" t="inlineStr">
         <is>
-          <t>十一月二日 (1949 後), 外洋陳和武寄潮汕李氏州妻</t>
+          <t>十一月二日（1949后），外洋陈和武寄潮汕李氏荆妻</t>
         </is>
       </c>
       <c r="E210" s="12" t="inlineStr">
@@ -11770,7 +11770,7 @@
       </c>
       <c r="D211" s="12" t="inlineStr">
         <is>
-          <t>十一月廿二(1949 后) ，香蔡得钦寄潮安登降都蔡永钦先生</t>
+          <t>十一月廿二（1949后），香蔡得钦寄潮安登隆都蔡永钦先生</t>
         </is>
       </c>
       <c r="E211" s="12" t="inlineStr">
@@ -11827,7 +11827,7 @@
       </c>
       <c r="D212" s="12" t="inlineStr">
         <is>
-          <t>十一月廿七日 (1949 后) ，外洋巧仙寄潮汕双亲大人</t>
+          <t>十一月廿七日（1949后），外洋巧仙寄潮汕双亲大人</t>
         </is>
       </c>
       <c r="E212" s="12" t="inlineStr">
@@ -11880,7 +11880,7 @@
       </c>
       <c r="D213" s="12" t="inlineStr">
         <is>
-          <t>农历十二月十二日 (1949 后) ，进黄凤权寄漆届南砂乡林宅岳母大人</t>
+          <t>农历十二月十二日（1949后），暹黄丙权寄澄邑南砂乡林宅岳母大人</t>
         </is>
       </c>
       <c r="E213" s="12" t="inlineStr">
@@ -11938,7 +11938,7 @@
       </c>
       <c r="D214" s="12" t="inlineStr">
         <is>
-          <t>(1949 后) 外洋张茂口寄潮汕祖母大人</t>
+          <t>（1949后）外洋张茂□寄潮汕祖母大人</t>
         </is>
       </c>
       <c r="E214" s="12" t="inlineStr">
